--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0008.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0008.xlsx
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Switching to Chisa's perspective</t>
+          <t>Chuyển sang góc nhìn của Chisa</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Switching to Denia's perspective</t>
+          <t>Chuyển sang góc nhìn của Denia</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Introduction of the Crownless</t>
+          <t>Giới thiệu về Crownless</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>The Crownless</t>
+          <t>Vị Vua Không Vương Miện</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Central Plains-Taoyuan Vale</t>
+          <t>Central Plains - Thung Lũng Đào Nguyên</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Shui</t>
+          <t>Thủy</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Chenpi</t>
+          <t>Trần Bì</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Doudou</t>
+          <t>Đậu Đậu</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Fuyan</t>
+          <t>Phù Diễn</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Ganxue</t>
+          <t>Cảm Huyết</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Guanghui</t>
+          <t>Quang Huy</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Gupan</t>
+          <t>Cổ Phan</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Huaijin</t>
+          <t>Hoài Cận</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Jifeng</t>
+          <t>Tế Phong</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
